--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1431,486 @@
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5,415</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>808424</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8,08,424</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>403309</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4,03,309</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2706</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2,706</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>405115</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4,05,115</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2709</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2,709</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1,149</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>201655</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2,01,655</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>104334</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1,04,334</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>576</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>97321</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>97,321</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>573</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -1532,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1588,6 +2068,25 @@
         <v>560</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>405115</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2709</v>
+      </c>
+      <c r="D3" t="n">
+        <v>97321</v>
+      </c>
+      <c r="E3" t="n">
+        <v>573</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily long" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Load factor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily long" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Load factor" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Traffic" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,763 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2660.67</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2652</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>397988</v>
+      </c>
+      <c r="E3" t="n">
+        <v>399206</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2660.67</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2661</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>396825.33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>400467</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5321.33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5313</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>794813.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>799673</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>568.33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>572</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>96749.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>99230</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>571.33</v>
+      </c>
+      <c r="E10" t="n">
+        <v>577</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>105218.67</v>
+      </c>
+      <c r="E11" t="n">
+        <v>108038</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1139.67</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>201968.33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>207268</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>68</v>
+      </c>
+      <c r="E18" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="E20" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>84.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>84.08</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1916,12 +2673,492 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5313</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5,313</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>799673</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7,99,673</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>400467</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4,00,467</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2661</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2,661</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>399206</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3,99,206</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2652</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2,652</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1,149</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>207268</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2,07,268</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>108038</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1,08,038</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>577</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>99230</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>99,230</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>572</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2006,13 +3243,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2087,6 +3324,25 @@
         <v>573</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>399206</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2652</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99230</v>
+      </c>
+      <c r="E4" t="n">
+        <v>572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2660.67</v>
+        <v>2671.75</v>
       </c>
       <c r="E2" t="n">
-        <v>2652</v>
+        <v>2705</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.33</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397988</v>
+        <v>399997.75</v>
       </c>
       <c r="E3" t="n">
-        <v>399206</v>
+        <v>406027</v>
       </c>
       <c r="F3" t="n">
-        <v>0.31</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2660.67</v>
+        <v>2671.5</v>
       </c>
       <c r="E4" t="n">
-        <v>2661</v>
+        <v>2704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396825.33</v>
+        <v>397984.5</v>
       </c>
       <c r="E5" t="n">
-        <v>400467</v>
+        <v>401462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5321.33</v>
+        <v>5343.25</v>
       </c>
       <c r="E6" t="n">
-        <v>5313</v>
+        <v>5409</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>1.23</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>794813.33</v>
+        <v>797982.25</v>
       </c>
       <c r="E7" t="n">
-        <v>799673</v>
+        <v>807489</v>
       </c>
       <c r="F7" t="n">
-        <v>0.61</v>
+        <v>1.19</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>568.33</v>
+        <v>572.75</v>
       </c>
       <c r="E8" t="n">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="F8" t="n">
-        <v>0.65</v>
+        <v>2.31</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96749.67</v>
+        <v>99390.25</v>
       </c>
       <c r="E9" t="n">
-        <v>99230</v>
+        <v>107312</v>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>7.97</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>571.33</v>
+        <v>571.5</v>
       </c>
       <c r="E10" t="n">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F10" t="n">
-        <v>0.99</v>
+        <v>0.09</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105218.67</v>
+        <v>105578.5</v>
       </c>
       <c r="E11" t="n">
-        <v>108038</v>
+        <v>106658</v>
       </c>
       <c r="F11" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1139.67</v>
+        <v>1144.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>201968.33</v>
+        <v>204968.75</v>
       </c>
       <c r="E13" t="n">
-        <v>207268</v>
+        <v>213970</v>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>4.39</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>87.2</v>
+        <v>90.75</v>
       </c>
       <c r="E14" t="n">
-        <v>87.2</v>
+        <v>94.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.84999999999999</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>88.84999999999999</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>47.55</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>47.1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72.22</v>
+        <v>75.8</v>
       </c>
       <c r="E17" t="n">
-        <v>72.22</v>
+        <v>79.37</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>81.5</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>16.56</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>92.31</v>
+        <v>94.33</v>
       </c>
       <c r="E19" t="n">
-        <v>92.31</v>
+        <v>96.34</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.53</v>
+        <v>82.56</v>
       </c>
       <c r="E20" t="n">
-        <v>82.53</v>
+        <v>82.58</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>86.2</v>
+        <v>86.05</v>
       </c>
       <c r="E21" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.7</v>
+        <v>86.7</v>
       </c>
       <c r="E22" t="n">
-        <v>84.7</v>
+        <v>88.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.08</v>
+        <v>85.89</v>
       </c>
       <c r="E23" t="n">
-        <v>84.08</v>
+        <v>87.7</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>8.26</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>92.55</v>
+        <v>92.12</v>
       </c>
       <c r="E25" t="n">
-        <v>92.55</v>
+        <v>91.7</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3153,6 +3153,966 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5409</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5,409</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>807489</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8,07,489</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>401462</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4,01,462</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2,704</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>406027</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4,06,027</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2705</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2,705</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1,158</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>213970</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2,13,970</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106658</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1,06,658</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>572</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>107312</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1,07,312</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>586</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>96.34%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>89.85%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>79.37</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>79.37%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>95</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>95.00%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>47.10%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>91.70%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>85.90%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>87.70%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>59</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>59.00%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>82.58%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>88.70%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3164,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3238,6 +4198,31 @@
         <v>84.7</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3249,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3343,6 +4328,25 @@
         <v>572</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>26 July 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>406027</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="D5" t="n">
+        <v>107312</v>
+      </c>
+      <c r="E5" t="n">
+        <v>586</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2671.75</v>
+        <v>2666.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2705</v>
+        <v>2647</v>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>-0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>399997.75</v>
+        <v>395855.8</v>
       </c>
       <c r="E3" t="n">
-        <v>406027</v>
+        <v>379288</v>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>-4.19</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2671.5</v>
+        <v>2665.8</v>
       </c>
       <c r="E4" t="n">
-        <v>2704</v>
+        <v>2643</v>
       </c>
       <c r="F4" t="n">
-        <v>1.22</v>
+        <v>-0.86</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>397984.5</v>
+        <v>394700</v>
       </c>
       <c r="E5" t="n">
-        <v>401462</v>
+        <v>381562</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>-3.33</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5343.25</v>
+        <v>5332.6</v>
       </c>
       <c r="E6" t="n">
-        <v>5409</v>
+        <v>5290</v>
       </c>
       <c r="F6" t="n">
-        <v>1.23</v>
+        <v>-0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>797982.25</v>
+        <v>790555.8</v>
       </c>
       <c r="E7" t="n">
-        <v>807489</v>
+        <v>760850</v>
       </c>
       <c r="F7" t="n">
-        <v>1.19</v>
+        <v>-3.76</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>572.75</v>
+        <v>571.4</v>
       </c>
       <c r="E8" t="n">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="F8" t="n">
-        <v>2.31</v>
+        <v>-0.95</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>99390.25</v>
+        <v>99653.2</v>
       </c>
       <c r="E9" t="n">
-        <v>107312</v>
+        <v>100705</v>
       </c>
       <c r="F9" t="n">
-        <v>7.97</v>
+        <v>1.06</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>571.5</v>
+        <v>570.8</v>
       </c>
       <c r="E10" t="n">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105578.5</v>
+        <v>104181.4</v>
       </c>
       <c r="E11" t="n">
-        <v>106658</v>
+        <v>98593</v>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>-5.36</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1144.25</v>
+        <v>1142.2</v>
       </c>
       <c r="E12" t="n">
-        <v>1158</v>
+        <v>1134</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>-0.72</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204968.75</v>
+        <v>203834.6</v>
       </c>
       <c r="E13" t="n">
-        <v>213970</v>
+        <v>199298</v>
       </c>
       <c r="F13" t="n">
-        <v>4.39</v>
+        <v>-2.23</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.75</v>
+        <v>92.47</v>
       </c>
       <c r="E14" t="n">
-        <v>94.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.91</v>
+        <v>3.71</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.34999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>89.84999999999999</v>
+        <v>92.83</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47.55</v>
+        <v>47.73</v>
       </c>
       <c r="E16" t="n">
-        <v>47.1</v>
+        <v>48.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.95</v>
+        <v>0.77</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>79.37</v>
+        <v>93.55</v>
       </c>
       <c r="F17" t="n">
-        <v>4.72</v>
+        <v>14.49</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81.5</v>
+        <v>77.33</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>16.56</v>
+        <v>-10.78</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.33</v>
+        <v>94.59</v>
       </c>
       <c r="E19" t="n">
-        <v>96.34</v>
+        <v>95.12</v>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.56</v>
+        <v>81.3</v>
       </c>
       <c r="E20" t="n">
-        <v>82.58</v>
+        <v>78.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03</v>
+        <v>-3.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>86.05</v>
+        <v>85.27</v>
       </c>
       <c r="E21" t="n">
-        <v>85.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.17</v>
+        <v>-1.84</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.7</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>88.7</v>
+        <v>81.8</v>
       </c>
       <c r="F22" t="n">
-        <v>2.31</v>
+        <v>-3.84</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85.89</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>87.7</v>
+        <v>81.92</v>
       </c>
       <c r="F23" t="n">
-        <v>2.11</v>
+        <v>-3.13</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>54.5</v>
+        <v>56.33</v>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>8.26</v>
+        <v>6.51</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>92.12</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>91.7</v>
+        <v>88.95</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.46</v>
+        <v>-2.32</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4113,6 +4113,966 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5290</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5,290</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>760850</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>7,60,850</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>381562</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>3,81,562</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2643</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2,643</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>379288</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3,79,288</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2647</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2,647</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1,134</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>199298</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1,99,298</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>98593</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>98,593</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>568</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100705</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1,00,705</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>566</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>95.12%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>92.83%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>93.55%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>69</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.00%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>95.90%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>48.10%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>88.95%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>83.70%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>81.92%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>60</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.00%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>78.80%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>81.80%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4124,7 +5084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4223,6 +5183,31 @@
         <v>88.7</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>81.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4234,7 +5219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4347,6 +5332,25 @@
         <v>586</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>379288</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2647</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100705</v>
+      </c>
+      <c r="E6" t="n">
+        <v>566</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2666.8</v>
+        <v>2645.33</v>
       </c>
       <c r="E2" t="n">
-        <v>2647</v>
+        <v>2538</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.74</v>
+        <v>-4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>395855.8</v>
+        <v>389958.17</v>
       </c>
       <c r="E3" t="n">
-        <v>379288</v>
+        <v>360470</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.19</v>
+        <v>-7.56</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2665.8</v>
+        <v>2643.33</v>
       </c>
       <c r="E4" t="n">
-        <v>2643</v>
+        <v>2531</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.86</v>
+        <v>-4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>394700</v>
+        <v>389336.67</v>
       </c>
       <c r="E5" t="n">
-        <v>381562</v>
+        <v>362520</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.33</v>
+        <v>-6.89</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5332.6</v>
+        <v>5288.67</v>
       </c>
       <c r="E6" t="n">
-        <v>5290</v>
+        <v>5069</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8</v>
+        <v>-4.15</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>790555.8</v>
+        <v>779294.83</v>
       </c>
       <c r="E7" t="n">
-        <v>760850</v>
+        <v>722990</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.76</v>
+        <v>-7.23</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>571.4</v>
+        <v>569.67</v>
       </c>
       <c r="E8" t="n">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.95</v>
+        <v>-1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>99653.2</v>
+        <v>99255.67</v>
       </c>
       <c r="E9" t="n">
-        <v>100705</v>
+        <v>97268</v>
       </c>
       <c r="F9" t="n">
-        <v>1.06</v>
+        <v>-2</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>570.8</v>
+        <v>568.83</v>
       </c>
       <c r="E10" t="n">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.49</v>
+        <v>-1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104181.4</v>
+        <v>103039.83</v>
       </c>
       <c r="E11" t="n">
-        <v>98593</v>
+        <v>97332</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.36</v>
+        <v>-5.54</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1142.2</v>
+        <v>1138.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.72</v>
+        <v>-1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>203834.6</v>
+        <v>202295.5</v>
       </c>
       <c r="E13" t="n">
-        <v>199298</v>
+        <v>194600</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.23</v>
+        <v>-3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.47</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>95.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>3.71</v>
+        <v>-1.19</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90.51000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="E15" t="n">
-        <v>92.83</v>
+        <v>94.66</v>
       </c>
       <c r="F15" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47.73</v>
+        <v>47.4</v>
       </c>
       <c r="E16" t="n">
-        <v>48.1</v>
+        <v>46.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0.77</v>
+        <v>-2.11</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81.70999999999999</v>
+        <v>82.56</v>
       </c>
       <c r="E17" t="n">
-        <v>93.55</v>
+        <v>85.08</v>
       </c>
       <c r="F17" t="n">
-        <v>14.49</v>
+        <v>3.06</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77.33</v>
+        <v>75.5</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.78</v>
+        <v>-7.28</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.59</v>
+        <v>94.69</v>
       </c>
       <c r="E19" t="n">
-        <v>95.12</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81.3</v>
+        <v>80.56</v>
       </c>
       <c r="E20" t="n">
-        <v>78.8</v>
+        <v>78.33</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.08</v>
+        <v>-2.77</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>85.27</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>83.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.84</v>
+        <v>-2.36</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.06999999999999</v>
+        <v>83.67</v>
       </c>
       <c r="E22" t="n">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.84</v>
+        <v>-4.99</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.56999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>81.92</v>
+        <v>80.69</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.13</v>
+        <v>-3.48</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56.33</v>
+        <v>57.5</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>6.51</v>
+        <v>6.09</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>91.06999999999999</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>88.95</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.32</v>
+        <v>-2.58</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5073,6 +5073,966 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5069</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>5,069</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>722990</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>7,22,990</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>362520</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>3,62,520</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2531</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2,531</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>360470</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>3,60,470</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2538</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2,538</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1,120</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>194600</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1,94,600</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>97332</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>97,332</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>559</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>97268</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>97,268</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>561</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>95</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>95.00%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>94.66%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>70</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>91</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>91.00%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>46.40%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>87.96%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>82.60%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>80.69%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>61</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>61.00%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>78.33%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>79.50%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5084,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5208,6 +6168,31 @@
         <v>81.8</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="G5" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5219,7 +6204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5351,6 +6336,25 @@
         <v>566</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>28 July 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>360470</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="D7" t="n">
+        <v>97268</v>
+      </c>
+      <c r="E7" t="n">
+        <v>561</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2645.33</v>
+        <v>2649</v>
       </c>
       <c r="E2" t="n">
-        <v>2538</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.06</v>
+        <v>0.83</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>389958.17</v>
+        <v>387978.14</v>
       </c>
       <c r="E3" t="n">
-        <v>360470</v>
+        <v>376098</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.56</v>
+        <v>-3.06</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2643.33</v>
+        <v>2647</v>
       </c>
       <c r="E4" t="n">
-        <v>2531</v>
+        <v>2669</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.25</v>
+        <v>0.83</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>389336.67</v>
+        <v>387500.57</v>
       </c>
       <c r="E5" t="n">
-        <v>362520</v>
+        <v>376484</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.89</v>
+        <v>-2.84</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5288.67</v>
+        <v>5296</v>
       </c>
       <c r="E6" t="n">
-        <v>5069</v>
+        <v>5340</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.15</v>
+        <v>0.83</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>779294.83</v>
+        <v>775478.71</v>
       </c>
       <c r="E7" t="n">
-        <v>722990</v>
+        <v>752582</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.23</v>
+        <v>-2.95</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>569.67</v>
+        <v>567.71</v>
       </c>
       <c r="E8" t="n">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.52</v>
+        <v>-2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>99255.67</v>
+        <v>99365.57000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>97268</v>
+        <v>100025</v>
       </c>
       <c r="F9" t="n">
-        <v>-2</v>
+        <v>0.66</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>568.83</v>
+        <v>566.5700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.73</v>
+        <v>-2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103039.83</v>
+        <v>102160.57</v>
       </c>
       <c r="E11" t="n">
-        <v>97332</v>
+        <v>96885</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.54</v>
+        <v>-5.16</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1138.5</v>
+        <v>1134.29</v>
       </c>
       <c r="E12" t="n">
-        <v>1120</v>
+        <v>1109</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.62</v>
+        <v>-2.23</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>202295.5</v>
+        <v>201526.14</v>
       </c>
       <c r="E13" t="n">
-        <v>194600</v>
+        <v>196910</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8</v>
+        <v>-2.29</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.09999999999999</v>
+        <v>92.42</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>93.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.19</v>
+        <v>1.38</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>91.55</v>
+        <v>92.41</v>
       </c>
       <c r="E15" t="n">
-        <v>94.66</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="E16" t="n">
         <v>46.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.11</v>
+        <v>-1.69</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.56</v>
+        <v>84.81</v>
       </c>
       <c r="E17" t="n">
-        <v>85.08</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>3.06</v>
+        <v>10.65</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.28</v>
+        <v>-5.91</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.69</v>
+        <v>94.36</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>93.02</v>
       </c>
       <c r="F19" t="n">
-        <v>0.32</v>
+        <v>-1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.56</v>
+        <v>80.16</v>
       </c>
       <c r="E20" t="n">
-        <v>78.33</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.77</v>
+        <v>-2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84.59999999999999</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.36</v>
+        <v>-2</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.67</v>
+        <v>81.84</v>
       </c>
       <c r="E22" t="n">
-        <v>79.5</v>
+        <v>74.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.99</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83.59999999999999</v>
+        <v>82.72</v>
       </c>
       <c r="E23" t="n">
-        <v>80.69</v>
+        <v>79.23</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.48</v>
+        <v>-4.22</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>57.5</v>
+        <v>58.2</v>
       </c>
       <c r="E24" t="n">
         <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>6.09</v>
+        <v>4.81</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>90.29000000000001</v>
+        <v>90.08</v>
       </c>
       <c r="E25" t="n">
-        <v>87.95999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.58</v>
+        <v>-0.91</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6033,6 +6033,966 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>5340</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>5,340</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>752582</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7,52,582</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>376484</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>3,76,484</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>2669</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2,669</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>376098</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3,76,098</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1109</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1,109</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>196910</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1,96,910</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>96885</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>96,885</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>553</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100025</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1,00,025</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>556</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>93.02%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>95.85%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>93.85%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>70</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>93.70%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>46.40%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>89.26000000000001</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>89.26%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>82.50%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>79.23%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>61</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.00%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>78.54%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>74.50%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6044,7 +7004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6193,6 +7153,31 @@
         <v>79.5</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>89.26000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6204,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6355,6 +7340,25 @@
         <v>561</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>29 July 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>376098</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2671</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100025</v>
+      </c>
+      <c r="E8" t="n">
+        <v>556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -422,13 +422,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,6 +451,486 @@
         <is>
           <t>avg</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>383755</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>382785</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5393</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>766540</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>108451</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>105543</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>213994</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>95.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>97.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>78.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>91.02</v>
       </c>
     </row>
   </sheetData>
@@ -464,17 +944,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,6 +996,966 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>76</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>49</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>582</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>593</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
         </is>
       </c>
     </row>
@@ -530,10 +1970,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,6 +1987,61 @@
         <is>
           <t>report_date</t>
         </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="C2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -554,10 +2055,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +2071,45 @@
           <t>report_date</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dom Departing Pax</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dom Departing flights</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Int Departing Pax</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Int Departing flights</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>383755</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>108451</v>
+      </c>
+      <c r="E2" t="n">
+        <v>593</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2698</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>383755</v>
+        <v>385058</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2695</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>382785</v>
+        <v>381952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5393</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>766540</v>
+        <v>767010</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>593</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108451</v>
+        <v>105553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105543</v>
+        <v>110647</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1175</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>213994</v>
+        <v>216200</v>
       </c>
     </row>
     <row r="14">
@@ -944,11 +944,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -1002,35 +1002,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97.44</v>
+        <v>5474</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,474</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1042,35 +1042,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95.38</v>
+        <v>767010</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,67,010</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1082,35 +1082,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>95.59999999999999</v>
+        <v>381952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,81,952</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1122,35 +1122,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>2728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,728</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1162,35 +1162,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>92.09999999999999</v>
+        <v>385058</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,85,058</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1202,35 +1202,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.7</v>
+        <v>2746</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,746</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1242,35 +1242,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>91.02</v>
+        <v>1161</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,161</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1282,35 +1282,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.8</v>
+        <v>216200</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,16,200</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1322,35 +1322,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>79.59999999999999</v>
+        <v>110647</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,10,647</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1362,35 +1362,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>582</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1402,35 +1402,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.45</v>
+        <v>105553</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,05,553</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1442,35 +1442,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>579</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1487,30 +1487,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1527,30 +1527,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1567,30 +1567,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1607,30 +1607,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1647,30 +1647,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1687,30 +1687,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1727,30 +1727,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1767,30 +1767,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1807,30 +1807,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1847,30 +1847,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1887,30 +1887,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1927,33 +1927,513 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>582</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E37" t="n">
         <v>593</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -2055,10 +2535,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -2095,19 +2575,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01 August 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>385058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2746</v>
+      </c>
+      <c r="D2" t="n">
+        <v>105553</v>
+      </c>
+      <c r="E2" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>383755</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>2698</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>108451</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2746</v>
+        <v>2794.5</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>385058</v>
+        <v>394195.5</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2728</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>381952</v>
+        <v>391627</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5474</v>
+        <v>5576.5</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>767010</v>
+        <v>785822.5</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105553</v>
+        <v>108919.5</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>582</v>
+        <v>588.5</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110647</v>
+        <v>111556</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1161</v>
+        <v>1177.5</v>
       </c>
     </row>
     <row r="13">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>216200</v>
+        <v>220475.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>95.38</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95.59999999999999</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -790,13 +790,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>97.44</v>
+        <v>89.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.45</v>
+        <v>79.56999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>83.8</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.59999999999999</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>91.02</v>
+        <v>89.54000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1482,35 +1482,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>97.44</v>
+        <v>5679</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,679</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1522,35 +1522,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>95.38</v>
+        <v>804635</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,04,635</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1562,35 +1562,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>95.59999999999999</v>
+        <v>401302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,01,302</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1602,35 +1602,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>2836</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,836</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1642,35 +1642,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>92.09999999999999</v>
+        <v>403333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,03,333</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1682,35 +1682,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40.7</v>
+        <v>2843</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,843</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1722,35 +1722,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>91.02</v>
+        <v>1194</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1762,35 +1762,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>83.8</v>
+        <v>224751</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,24,751</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1802,35 +1802,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>79.59999999999999</v>
+        <v>112465</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,12,465</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1842,35 +1842,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>595</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>595</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1882,35 +1882,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>78.45</v>
+        <v>112286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,12,286</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1922,35 +1922,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>599</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1962,35 +1962,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5393</v>
+        <v>89.77</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.77%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2002,35 +2002,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>766540</v>
+        <v>87.61</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>87.61%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2042,35 +2042,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>382785</v>
+        <v>68.75</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>68.75%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2082,35 +2082,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2695</v>
+        <v>46</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>46.00%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2122,35 +2122,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>383755</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>90.90%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2162,35 +2162,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2698</v>
+        <v>47.1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>47.10%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2202,35 +2202,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1175</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>89.54%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2242,35 +2242,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>213994</v>
+        <v>77.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2282,35 +2282,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105543</v>
+        <v>82.61</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>82.61%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2322,35 +2322,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>582</v>
+        <v>61</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>61.00%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2362,35 +2362,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>02 August 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>108451</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.57%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2402,38 +2402,998 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>02 August 2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>79.20%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>76</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>49</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>80</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>582</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E61" t="n">
         <v>593</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -2450,10 +3410,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -2502,25 +3462,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02 August 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="E2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>91.02</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>83.8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>49</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>78.45</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2535,7 +3520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2594,19 +3579,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02 August 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>403333</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2843</v>
+      </c>
+      <c r="D3" t="n">
+        <v>112286</v>
+      </c>
+      <c r="E3" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>383755</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>2698</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>108451</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2794.5</v>
+        <v>2795.67</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>394195.5</v>
+        <v>389447.33</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2782</v>
+        <v>2786.67</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391627</v>
+        <v>388532.33</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5576.5</v>
+        <v>5582.33</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>785822.5</v>
+        <v>777979.67</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>589</v>
+        <v>587.67</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108919.5</v>
+        <v>107516</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>588.5</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>111556</v>
+        <v>110133.33</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1177.5</v>
+        <v>1176.67</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>220475.5</v>
+        <v>217649.33</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.61</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68.75</v>
+        <v>73.55</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>89.77</v>
+        <v>92.04000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.56999999999999</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.2</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82.61</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>89.54000000000001</v>
+        <v>88.09</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2442,35 +2442,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>97.44</v>
+        <v>5594</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,594</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2482,35 +2482,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>95.38</v>
+        <v>762294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,62,294</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2522,35 +2522,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>95.59999999999999</v>
+        <v>382343</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,82,343</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2562,35 +2562,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>76</v>
+        <v>2796</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,796</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2602,35 +2602,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>92.09999999999999</v>
+        <v>379951</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,79,951</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2642,35 +2642,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>40.7</v>
+        <v>2798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,798</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2682,35 +2682,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>91.02</v>
+        <v>1175</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2722,35 +2722,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>83.8</v>
+        <v>211997</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,11,997</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2762,35 +2762,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>79.59999999999999</v>
+        <v>107288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,07,288</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2802,35 +2802,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>49</v>
+        <v>590</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>590</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2842,35 +2842,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>78.45</v>
+        <v>104709</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,04,709</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2882,35 +2882,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>585</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2922,35 +2922,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5393</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>94.32%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2962,35 +2962,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>766540</v>
+        <v>83.53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>83.53%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3002,35 +3002,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>382785</v>
+        <v>78.34</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>78.34%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3042,35 +3042,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2695</v>
+        <v>54</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>54.00%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3082,35 +3082,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>383755</v>
+        <v>89.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>89.50%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3122,35 +3122,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2698</v>
+        <v>48.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>48.30%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3162,35 +3162,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1175</v>
+        <v>86.63</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>86.63%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3202,35 +3202,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>213994</v>
+        <v>77.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3242,35 +3242,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105543</v>
+        <v>77.11</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>77.11%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3282,35 +3282,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>582</v>
+        <v>62</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>62.00%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3322,35 +3322,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>108451</v>
+        <v>74.95</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>74.95%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3362,38 +3362,998 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>03 August 2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>82.10%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>76</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>49</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>80</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>582</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E85" t="n">
         <v>593</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -3410,7 +4370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3487,25 +4447,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03 August 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="G3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>91.02</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>83.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>49</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>78.45</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>80</v>
       </c>
     </row>
@@ -3520,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3598,19 +4583,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03 August 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>379951</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2798</v>
+      </c>
+      <c r="D4" t="n">
+        <v>104709</v>
+      </c>
+      <c r="E4" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>383755</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>2698</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>108451</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2795.67</v>
+        <v>2769.5</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>389447.33</v>
+        <v>383614.75</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2786.67</v>
+        <v>2764.5</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>388532.33</v>
+        <v>383055.5</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5582.33</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>777979.67</v>
+        <v>766670.25</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>587.67</v>
+        <v>578.75</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107516</v>
+        <v>105132</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>589</v>
+        <v>581.25</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110133.33</v>
+        <v>107187.75</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1176.67</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>217649.33</v>
+        <v>212319.75</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.2</v>
+        <v>90.63</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.56999999999999</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47.7</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73.55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>92.04000000000001</v>
+        <v>91.98</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.26000000000001</v>
+        <v>76.70999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.5</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80.65000000000001</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.86</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>88.09</v>
+        <v>87.48999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3402,35 +3402,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>97.44</v>
+        <v>5389</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,389</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3442,35 +3442,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>95.38</v>
+        <v>732742</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,32,742</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3482,35 +3482,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>95.59999999999999</v>
+        <v>366625</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,66,625</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3522,35 +3522,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>76</v>
+        <v>2698</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3562,35 +3562,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>92.09999999999999</v>
+        <v>366117</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,66,117</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3602,35 +3602,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>40.7</v>
+        <v>2691</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,691</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3642,35 +3642,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>91.02</v>
+        <v>1110</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,110</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3682,35 +3682,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>83.8</v>
+        <v>196331</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>1,96,331</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3722,35 +3722,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>79.59999999999999</v>
+        <v>98351</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>98,351</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3762,35 +3762,35 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>558</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>558</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3802,35 +3802,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>78.45</v>
+        <v>97980</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>97,980</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3842,35 +3842,35 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3882,35 +3882,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5393</v>
+        <v>91.86</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>91.86%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3922,35 +3922,35 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>766540</v>
+        <v>82.39</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>82.39%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3962,35 +3962,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>382785</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>83.90%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4002,35 +4002,35 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2695</v>
+        <v>56</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>56.00%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4042,35 +4042,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>383755</v>
+        <v>91.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>91.50%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4082,35 +4082,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2698</v>
+        <v>42.9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>42.90%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4122,35 +4122,35 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1175</v>
+        <v>86.31</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>86.31%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4162,35 +4162,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>213994</v>
+        <v>72</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4202,35 +4202,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>105543</v>
+        <v>78.03</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>78.03%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4242,35 +4242,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>582</v>
+        <v>60</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4282,35 +4282,35 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>108451</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>75.60%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4322,38 +4322,998 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>04 August 2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>85</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>85.00%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>76</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>49</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>80</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>582</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E109" t="n">
         <v>593</v>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -4370,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4472,25 +5432,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>04 August 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>91.02</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>83.8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>49</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>78.45</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4505,7 +5490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4602,19 +5587,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>04 August 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>366117</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2691</v>
+      </c>
+      <c r="D5" t="n">
+        <v>97980</v>
+      </c>
+      <c r="E5" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>383755</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>2698</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>108451</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2769.5</v>
+        <v>2774.6</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>383614.75</v>
+        <v>385700</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2764.5</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>383055.5</v>
+        <v>385058.4</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5534</v>
+        <v>5544.6</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>766670.25</v>
+        <v>770758.4</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>578.75</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105132</v>
+        <v>105116.8</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>581.25</v>
+        <v>578.4</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>107187.75</v>
+        <v>105905</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1160</v>
+        <v>1154.4</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212319.75</v>
+        <v>211021.8</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.63</v>
+        <v>90.84999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.51000000000001</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46.1</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.98</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76.70999999999999</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75.67</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.09999999999999</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.25</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.48999999999999</v>
+        <v>88.08</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4362,35 +4362,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>97.44</v>
+        <v>5587</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,587</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4402,35 +4402,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>95.38</v>
+        <v>787111</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,87,111</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4442,35 +4442,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>95.59999999999999</v>
+        <v>393070</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,93,070</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4482,35 +4482,35 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>76</v>
+        <v>2792</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,792</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4522,35 +4522,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>92.09999999999999</v>
+        <v>394041</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,94,041</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4562,35 +4562,35 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>40.7</v>
+        <v>2795</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,795</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4602,35 +4602,35 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>91.02</v>
+        <v>1132</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,132</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4642,35 +4642,35 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>83.8</v>
+        <v>205830</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,05,830</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4682,35 +4682,35 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>79.59999999999999</v>
+        <v>100774</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,00,774</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4722,35 +4722,35 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>49</v>
+        <v>567</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>567</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4762,35 +4762,35 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>78.45</v>
+        <v>105056</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,05,056</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4802,35 +4802,35 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>565</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4842,35 +4842,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5393</v>
+        <v>91.3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>91.30%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4882,35 +4882,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>766540</v>
+        <v>90.59</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>90.59%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4922,35 +4922,35 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>382785</v>
+        <v>87</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>87.00%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4962,35 +4962,35 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2695</v>
+        <v>90</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>90.00%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5002,35 +5002,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>383755</v>
+        <v>91.5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>91.50%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5042,35 +5042,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2698</v>
+        <v>43.3</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>43.30%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5082,35 +5082,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1175</v>
+        <v>89.83</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>89.83%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5122,35 +5122,35 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>213994</v>
+        <v>79</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>79.00%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5162,35 +5162,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105543</v>
+        <v>79.39</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.39%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5202,35 +5202,35 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>582</v>
+        <v>65</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5242,35 +5242,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>108451</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5282,38 +5282,998 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>05 August 2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>87.20%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>76</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>49</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>80</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>582</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="E133" t="n">
         <v>593</v>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -5330,7 +6290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5457,25 +6417,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05 August 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>89.83</v>
+      </c>
+      <c r="C5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="E5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>91.02</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>83.8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>49</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>78.45</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5490,7 +6475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5606,19 +6591,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05 August 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>394041</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2795</v>
+      </c>
+      <c r="D6" t="n">
+        <v>105056</v>
+      </c>
+      <c r="E6" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>383755</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>2698</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>108451</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2774.6</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>385700</v>
+        <v>386938.17</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2770</v>
+        <v>2769.5</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>385058.4</v>
+        <v>386371.33</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5544.6</v>
+        <v>5545.5</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>770758.4</v>
+        <v>773309.5</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>576</v>
+        <v>573.33</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105116.8</v>
+        <v>104732.83</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>578.4</v>
+        <v>575.33</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105905</v>
+        <v>104754.67</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1154.4</v>
+        <v>1148.67</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211021.8</v>
+        <v>209487.5</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.84999999999999</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86.03</v>
+        <v>84.58</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45.4</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79.5</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61.5</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.81</v>
+        <v>91.31</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.3</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.38</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.28</v>
+        <v>79.09</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>88.08</v>
+        <v>88.3</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5322,35 +5322,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>97.44</v>
+        <v>5550</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,550</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5362,35 +5362,35 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>95.38</v>
+        <v>786065</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,86,065</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5402,35 +5402,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>95.59999999999999</v>
+        <v>392936</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,92,936</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5442,35 +5442,35 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>76</v>
+        <v>2767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,767</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5482,35 +5482,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>92.09999999999999</v>
+        <v>393129</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,93,129</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5522,35 +5522,35 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>40.7</v>
+        <v>2783</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,783</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5562,35 +5562,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>91.02</v>
+        <v>1120</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,120</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5602,35 +5602,35 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>83.8</v>
+        <v>201816</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,01,816</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5642,35 +5642,35 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>79.59999999999999</v>
+        <v>99003</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>99,003</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5682,35 +5682,35 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>49</v>
+        <v>560</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5722,35 +5722,35 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>78.45</v>
+        <v>102813</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,02,813</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5762,35 +5762,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5802,35 +5802,35 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5393</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.29%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5842,35 +5842,35 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>766540</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>78.76%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5882,35 +5882,35 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>382785</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>82.24%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5922,35 +5922,35 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2695</v>
+        <v>85</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5962,35 +5962,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>383755</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>85.40%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6002,35 +6002,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2698</v>
+        <v>45.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>45.50%</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6042,35 +6042,35 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1175</v>
+        <v>89.19</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>89.19%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6082,35 +6082,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>213994</v>
+        <v>79</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>79.00%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6122,35 +6122,35 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>105543</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>78.32%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6162,35 +6162,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>582</v>
+        <v>45</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6202,35 +6202,35 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>06 August 2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>108451</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.15%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6242,38 +6242,998 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>06 August 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>86</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>86.00%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>76</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>49</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>80</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>582</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="E157" t="n">
         <v>593</v>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -6290,7 +7250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6442,25 +7402,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06 August 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="C6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>91.02</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>83.8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>49</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>78.45</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6475,7 +7460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6610,19 +7595,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06 August 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>393129</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2783</v>
+      </c>
+      <c r="D7" t="n">
+        <v>102813</v>
+      </c>
+      <c r="E7" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>383755</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>2698</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>108451</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2776</v>
+        <v>2781.29</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>386938.17</v>
+        <v>389515.86</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2769.5</v>
+        <v>2774.57</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>386371.33</v>
+        <v>388566.57</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5545.5</v>
+        <v>5555.86</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>773309.5</v>
+        <v>778082.4300000001</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>573.33</v>
+        <v>576.29</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>104732.83</v>
+        <v>105594.43</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>575.33</v>
+        <v>578.4299999999999</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104754.67</v>
+        <v>105015.71</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1148.67</v>
+        <v>1154.71</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>209487.5</v>
+        <v>210610.14</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6282,35 +6282,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>97.44</v>
+        <v>5618</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,618</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6322,35 +6322,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>95.38</v>
+        <v>806720</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,06,720</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6362,35 +6362,35 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>95.59999999999999</v>
+        <v>401738</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,01,738</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6402,35 +6402,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>76</v>
+        <v>2805</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,805</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6442,35 +6442,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>92.09999999999999</v>
+        <v>404982</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,04,982</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6482,35 +6482,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>40.7</v>
+        <v>2813</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,813</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6522,35 +6522,35 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>91.02</v>
+        <v>1191</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,191</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6562,35 +6562,35 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>83.8</v>
+        <v>217346</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,17,346</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6602,35 +6602,35 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>79.59999999999999</v>
+        <v>106582</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,06,582</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6642,35 +6642,35 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>49</v>
+        <v>597</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6682,35 +6682,35 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>78.45</v>
+        <v>110764</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,10,764</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6722,35 +6722,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>80</v>
+        <v>594</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>594</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6767,30 +6767,30 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6807,30 +6807,30 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6847,30 +6847,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6887,30 +6887,30 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6927,30 +6927,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6967,30 +6967,30 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7007,30 +7007,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7047,30 +7047,30 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7087,30 +7087,30 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7127,30 +7127,30 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7167,30 +7167,30 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7207,33 +7207,513 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>80</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>582</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E157" t="n">
+      <c r="E169" t="n">
         <v>593</v>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -7460,7 +7940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7614,19 +8094,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07 August 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>404982</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2813</v>
+      </c>
+      <c r="D8" t="n">
+        <v>110764</v>
+      </c>
+      <c r="E8" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>383755</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>2698</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>108451</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2781.29</v>
+        <v>2782.12</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>389515.86</v>
+        <v>390822.25</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2774.57</v>
+        <v>2778.38</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>388566.57</v>
+        <v>390391.75</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5555.86</v>
+        <v>5560.5</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>778082.4300000001</v>
+        <v>781214</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>576.29</v>
+        <v>579.12</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105594.43</v>
+        <v>106462.12</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>578.4299999999999</v>
+        <v>580.88</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105015.71</v>
+        <v>105555.5</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1154.71</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210610.14</v>
+        <v>212017.62</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6762,35 +6762,35 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>97.44</v>
+        <v>5593</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,593</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6802,35 +6802,35 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>95.38</v>
+        <v>803135</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,03,135</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6842,35 +6842,35 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>95.59999999999999</v>
+        <v>403168</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,03,168</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6882,35 +6882,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>76</v>
+        <v>2805</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,805</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6922,35 +6922,35 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>92.09999999999999</v>
+        <v>399967</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,99,967</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6962,35 +6962,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>40.7</v>
+        <v>2788</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7002,35 +7002,35 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>91.02</v>
+        <v>1197</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,197</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7042,35 +7042,35 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>83.8</v>
+        <v>221870</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,21,870</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7082,35 +7082,35 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>79.59999999999999</v>
+        <v>109334</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,09,334</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7122,35 +7122,35 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>49</v>
+        <v>598</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>598</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7162,35 +7162,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>78.45</v>
+        <v>112536</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,12,536</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7202,35 +7202,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>599</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7247,30 +7247,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7327,30 +7327,30 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7367,30 +7367,30 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7407,30 +7407,30 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7447,30 +7447,30 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7487,30 +7487,30 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7527,30 +7527,30 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7567,30 +7567,30 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7607,30 +7607,30 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7647,30 +7647,30 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7687,33 +7687,513 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>80</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>582</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E169" t="n">
+      <c r="E181" t="n">
         <v>593</v>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -7940,7 +8420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8113,19 +8593,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08 August 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>399967</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="D9" t="n">
+        <v>112536</v>
+      </c>
+      <c r="E9" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>383755</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>2698</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>108451</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2782.12</v>
+        <v>2784.56</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>390822.25</v>
+        <v>390765.44</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2778.38</v>
+        <v>2780.78</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>390391.75</v>
+        <v>390781.33</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5560.5</v>
+        <v>5565.33</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>781214</v>
+        <v>781546.78</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>579.12</v>
+        <v>578.89</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106462.12</v>
+        <v>106487.22</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>580.88</v>
+        <v>581.89</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105555.5</v>
+        <v>105125.11</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1160</v>
+        <v>1160.78</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212017.62</v>
+        <v>211612.33</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.76000000000001</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.58</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45.42</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.05</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.2</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.31</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.67</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.90000000000001</v>
+        <v>84.63</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.09</v>
+        <v>78.86</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58.6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>88.3</v>
+        <v>87.86</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7242,35 +7242,35 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>97.44</v>
+        <v>5604</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,604</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7282,35 +7282,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>95.38</v>
+        <v>784209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,84,209</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7322,35 +7322,35 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>95.59999999999999</v>
+        <v>393898</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,93,898</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7362,35 +7362,35 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>76</v>
+        <v>2800</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7402,35 +7402,35 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>92.09999999999999</v>
+        <v>390311</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,90,311</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7442,35 +7442,35 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>40.7</v>
+        <v>2804</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,804</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7482,35 +7482,35 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>91.02</v>
+        <v>1167</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,167</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7522,35 +7522,35 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>83.8</v>
+        <v>208370</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,08,370</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7562,35 +7562,35 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>79.59999999999999</v>
+        <v>101682</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,01,682</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7602,35 +7602,35 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>49</v>
+        <v>590</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>590</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7642,35 +7642,35 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>78.45</v>
+        <v>106688</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,06,688</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7682,35 +7682,35 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>80</v>
+        <v>577</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>577</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7722,35 +7722,35 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5393</v>
+        <v>89.89</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.89%</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7762,35 +7762,35 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>766540</v>
+        <v>81.89</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>81.89%</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7802,35 +7802,35 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>382785</v>
+        <v>79.09</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>79.09%</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7842,35 +7842,35 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2695</v>
+        <v>67</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>67.00%</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7882,35 +7882,35 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>383755</v>
+        <v>88.7</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>88.70%</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7922,35 +7922,35 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2698</v>
+        <v>41.4</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.40%</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7962,35 +7962,35 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1175</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>85.65%</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8002,35 +8002,35 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>213994</v>
+        <v>79</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>79.00%</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8042,35 +8042,35 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>105543</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>77.68%</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8082,35 +8082,35 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>582</v>
+        <v>61</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>61.00%</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8122,35 +8122,35 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>108451</v>
+        <v>77.91</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>77.91%</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8162,38 +8162,998 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10 August 2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>88.30%</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>76</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>49</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>80</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>582</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E181" t="n">
+      <c r="E205" t="n">
         <v>593</v>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -8210,7 +9170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8387,25 +9347,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10 August 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D7" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77.91</v>
+      </c>
+      <c r="G7" t="n">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>91.02</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>83.8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>49</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>78.45</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>80</v>
       </c>
     </row>
@@ -8420,7 +9405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8612,19 +9597,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>10 August 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>390311</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2804</v>
+      </c>
+      <c r="D10" t="n">
+        <v>106688</v>
+      </c>
+      <c r="E10" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>383755</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>2698</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>108451</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2784.56</v>
+        <v>2782.7</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>390765.44</v>
+        <v>390373.8</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2780.78</v>
+        <v>2778.4</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>390781.33</v>
+        <v>389739.6</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5565.33</v>
+        <v>5561.1</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>781546.78</v>
+        <v>780113.4</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>578.89</v>
+        <v>579.4</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106487.22</v>
+        <v>106836.6</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>581.89</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105125.11</v>
+        <v>103981.6</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1160.78</v>
+        <v>1161.4</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211612.33</v>
+        <v>210818.2</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.58</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.13</v>
+        <v>84.97</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.75</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79.89</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.33</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.06999999999999</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.33</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.63</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78.86</v>
+        <v>78.91</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>60.43</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.86</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8202,35 +8202,35 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>97.44</v>
+        <v>5523</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,523</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8242,35 +8242,35 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>95.38</v>
+        <v>767213</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,67,213</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8282,35 +8282,35 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>95.59999999999999</v>
+        <v>380364</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,80,364</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8322,35 +8322,35 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>76</v>
+        <v>2757</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,757</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8362,35 +8362,35 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>92.09999999999999</v>
+        <v>386849</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,86,849</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8402,35 +8402,35 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>40.7</v>
+        <v>2766</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,766</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8442,35 +8442,35 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>91.02</v>
+        <v>1167</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,167</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8482,35 +8482,35 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>83.8</v>
+        <v>203671</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,03,671</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8522,35 +8522,35 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>79.59999999999999</v>
+        <v>93690</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>93,690</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8562,35 +8562,35 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>49</v>
+        <v>583</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>583</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8602,35 +8602,35 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>78.45</v>
+        <v>109981</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,09,981</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8642,35 +8642,35 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>80</v>
+        <v>584</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>584</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8682,35 +8682,35 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5393</v>
+        <v>93.55</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>93.55%</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8722,35 +8722,35 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>766540</v>
+        <v>90.03</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>90.03%</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -8762,35 +8762,35 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>382785</v>
+        <v>82.45</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>82.45%</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2695</v>
+        <v>92</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>92.00%</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -8842,35 +8842,35 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8882,35 +8882,35 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2698</v>
+        <v>41.4</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.40%</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -8922,35 +8922,35 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1175</v>
+        <v>85.05</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>85.05%</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8962,35 +8962,35 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>213994</v>
+        <v>76.8</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>76.80%</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9002,35 +9002,35 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>105543</v>
+        <v>79.22</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.22%</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9042,35 +9042,35 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>582</v>
+        <v>69</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>69.00%</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9082,35 +9082,35 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>12 August 2026</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>108451</v>
+        <v>77.7</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>77.70%</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9122,38 +9122,998 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>12 August 2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>76</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>49</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>80</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>582</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E205" t="n">
+      <c r="E229" t="n">
         <v>593</v>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -9170,7 +10130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9372,25 +10332,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12 August 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="C8" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>91.02</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>83.8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>49</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>78.45</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>80</v>
       </c>
     </row>
@@ -9405,7 +10390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9616,19 +10601,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>12 August 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>386849</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2766</v>
+      </c>
+      <c r="D11" t="n">
+        <v>109981</v>
+      </c>
+      <c r="E11" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>383755</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>2698</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>108451</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2782.7</v>
+        <v>2787.73</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>390373.8</v>
+        <v>392151.45</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2778.4</v>
+        <v>2783.45</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>389739.6</v>
+        <v>391392.73</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5561.1</v>
+        <v>5571.18</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>780113.4</v>
+        <v>783544.1800000001</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>579.4</v>
+        <v>581.36</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106836.6</v>
+        <v>107252.82</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>582</v>
+        <v>583.73</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103981.6</v>
+        <v>103589.18</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1161.4</v>
+        <v>1165.09</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210818.2</v>
+        <v>210842</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.94</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.27</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.25</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.43000000000001</v>
+        <v>91.17</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.70999999999999</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.26000000000001</v>
+        <v>76.98999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.91</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78.91</v>
+        <v>78.97</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.45999999999999</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9162,12 +9162,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9181,11 +9181,11 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>97.44</v>
+        <v>89.41</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>89.41%</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9202,12 +9202,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9221,11 +9221,11 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>95.38</v>
+        <v>85.84</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>85.84%</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -9242,12 +9242,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9261,11 +9261,11 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>95.59999999999999</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>86.79%</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -9282,12 +9282,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9301,11 +9301,11 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>98.00%</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9322,12 +9322,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9341,11 +9341,11 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>92.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>88.80%</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -9362,12 +9362,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9381,11 +9381,11 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>40.7</v>
+        <v>43.5</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>43.50%</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -9402,12 +9402,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9421,11 +9421,11 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>91.02</v>
+        <v>87.02</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>87.02%</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -9442,12 +9442,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9461,11 +9461,11 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>83.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>75.10%</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -9482,12 +9482,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9501,11 +9501,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>79.40%</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -9522,12 +9522,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9562,12 +9562,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9581,11 +9581,11 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>78.45</v>
+        <v>78.78</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>78.78%</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -9602,12 +9602,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9621,11 +9621,11 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>80</v>
+        <v>84.3</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>84.30%</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9642,12 +9642,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9661,11 +9661,11 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5393</v>
+        <v>5672</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>5,672</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9682,12 +9682,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9701,11 +9701,11 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>766540</v>
+        <v>817852</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>8,17,852</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9722,12 +9722,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9741,11 +9741,11 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>382785</v>
+        <v>407924</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>4,07,924</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9762,12 +9762,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9781,11 +9781,11 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2695</v>
+        <v>2834</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>2,834</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9802,12 +9802,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9821,11 +9821,11 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>383755</v>
+        <v>409928</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>4,09,928</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9842,12 +9842,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9861,11 +9861,11 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2698</v>
+        <v>2838</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>2,838</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9882,12 +9882,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9901,11 +9901,11 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1175</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>1,202</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9922,12 +9922,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9941,11 +9941,11 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>213994</v>
+        <v>211080</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>2,11,080</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9962,12 +9962,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9981,11 +9981,11 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>105543</v>
+        <v>99665</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>99,665</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -10002,12 +10002,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10021,11 +10021,11 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>601</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -10042,12 +10042,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10061,11 +10061,11 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>108451</v>
+        <v>111415</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>1,11,415</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -10082,38 +10082,998 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>14 August 2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>601</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>76</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>49</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>80</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>582</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E229" t="n">
+      <c r="E253" t="n">
         <v>593</v>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -10130,7 +11090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10357,25 +11317,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.02</v>
+        <v>87.02</v>
       </c>
       <c r="C9" t="n">
-        <v>83.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
       </c>
       <c r="F9" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="G9" t="n">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="C10" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49</v>
+      </c>
+      <c r="F10" t="n">
         <v>78.45</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>80</v>
       </c>
     </row>
@@ -10390,7 +11375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10620,19 +11605,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>14 August 2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>409928</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2838</v>
+      </c>
+      <c r="D12" t="n">
+        <v>111415</v>
+      </c>
+      <c r="E12" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>383755</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>2698</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>108451</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2787.73</v>
+        <v>2788.33</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>392151.45</v>
+        <v>391380.92</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2783.45</v>
+        <v>2785.25</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391392.73</v>
+        <v>391093.33</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5571.18</v>
+        <v>5573.58</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>783544.1800000001</v>
+        <v>782474.25</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>581.36</v>
+        <v>582.42</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107252.82</v>
+        <v>107770.42</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>583.73</v>
+        <v>585.08</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103589.18</v>
+        <v>103447.83</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1165.09</v>
+        <v>1167.5</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210842</v>
+        <v>211218.25</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10122,35 +10122,35 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>97.44</v>
+        <v>5600</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,600</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10162,35 +10162,35 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>95.38</v>
+        <v>770705</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,70,705</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10202,35 +10202,35 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>95.59999999999999</v>
+        <v>387800</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,87,800</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10242,35 +10242,35 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>76</v>
+        <v>2805</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,805</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10282,35 +10282,35 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>92.09999999999999</v>
+        <v>382905</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,82,905</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10322,35 +10322,35 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>40.7</v>
+        <v>2795</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,795</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10362,35 +10362,35 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>91.02</v>
+        <v>1194</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,194</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10402,35 +10402,35 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>83.8</v>
+        <v>215357</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,15,357</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10442,35 +10442,35 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>79.59999999999999</v>
+        <v>101893</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>1,01,893</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10482,35 +10482,35 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>49</v>
+        <v>600</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10522,35 +10522,35 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>78.45</v>
+        <v>113464</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,13,464</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -10562,35 +10562,35 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>80</v>
+        <v>594</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>594</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -10607,30 +10607,30 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -10647,30 +10647,30 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -10687,30 +10687,30 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -10727,30 +10727,30 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -10767,30 +10767,30 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -10807,30 +10807,30 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -10847,30 +10847,30 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -10887,30 +10887,30 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -10927,30 +10927,30 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -10967,30 +10967,30 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11007,30 +11007,30 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11047,33 +11047,513 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>80</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>582</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E253" t="n">
+      <c r="E265" t="n">
         <v>593</v>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F265" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -11375,7 +11855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11624,19 +12104,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>15 August 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>382905</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2795</v>
+      </c>
+      <c r="D13" t="n">
+        <v>113464</v>
+      </c>
+      <c r="E13" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>383755</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>2698</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>108451</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2788.33</v>
+        <v>2787.77</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>391380.92</v>
+        <v>392113.62</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2785.25</v>
+        <v>2783.46</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391093.33</v>
+        <v>391719.15</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5573.58</v>
+        <v>5571.23</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>782474.25</v>
+        <v>783832.77</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>582.42</v>
+        <v>583.38</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107770.42</v>
+        <v>107933.15</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>585.08</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103447.83</v>
+        <v>102801.54</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1167.5</v>
+        <v>1170.38</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211218.25</v>
+        <v>210734.69</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.8</v>
+        <v>90.16</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.08</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.17</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81.06999999999999</v>
+        <v>81.98</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.5</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.17</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.84</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76.98999999999999</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.95999999999999</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78.97</v>
+        <v>79.39</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>59.33</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.40000000000001</v>
+        <v>87.28</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10602,35 +10602,35 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>97.44</v>
+        <v>5543</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,543</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -10642,35 +10642,35 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>95.38</v>
+        <v>800135</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,00,135</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -10682,35 +10682,35 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>95.59999999999999</v>
+        <v>399229</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,99,229</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -10722,35 +10722,35 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>76</v>
+        <v>2762</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,762</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -10762,35 +10762,35 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>92.09999999999999</v>
+        <v>400906</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,00,906</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -10802,35 +10802,35 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>40.7</v>
+        <v>2781</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,781</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -10842,35 +10842,35 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>91.02</v>
+        <v>1205</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,205</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -10882,35 +10882,35 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>83.8</v>
+        <v>204932</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,04,932</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -10922,35 +10922,35 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>79.59999999999999</v>
+        <v>95046</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>95,046</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -10962,35 +10962,35 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>49</v>
+        <v>610</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11002,35 +11002,35 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>78.45</v>
+        <v>109886</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,09,886</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11042,35 +11042,35 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>80</v>
+        <v>595</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>595</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11082,35 +11082,35 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5393</v>
+        <v>84.27</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>84.27%</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11122,35 +11122,35 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>766540</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>85.54%</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11162,35 +11162,35 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>382785</v>
+        <v>89.3</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>89.30%</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11202,35 +11202,35 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2695</v>
+        <v>77</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>77.00%</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11242,35 +11242,35 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>383755</v>
+        <v>93</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11282,35 +11282,35 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>2698</v>
+        <v>40.9</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.90%</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11322,35 +11322,35 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1175</v>
+        <v>86.3</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>86.30%</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11362,35 +11362,35 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>213994</v>
+        <v>79.3</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>79.30%</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11402,35 +11402,35 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>105543</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>82.76%</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -11442,35 +11442,35 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>582</v>
+        <v>62</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>62.00%</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -11482,35 +11482,35 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>108451</v>
+        <v>80.3</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>80.30%</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -11522,38 +11522,998 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>17 August 2026</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>76</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>49</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>80</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>582</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E265" t="n">
+      <c r="E289" t="n">
         <v>593</v>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -11570,7 +12530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11822,25 +12782,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17 August 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>91.02</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>83.8</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>49</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>78.45</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>80</v>
       </c>
     </row>
@@ -11855,7 +12840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12123,19 +13108,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>17 August 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>400906</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2781</v>
+      </c>
+      <c r="D14" t="n">
+        <v>109886</v>
+      </c>
+      <c r="E14" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>383755</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>2698</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>108451</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2787.77</v>
+        <v>2779.57</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>392113.62</v>
+        <v>392089.71</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2783.46</v>
+        <v>2776.29</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391719.15</v>
+        <v>391457.29</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5571.23</v>
+        <v>5555.86</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>783832.77</v>
+        <v>783547</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>583.38</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107933.15</v>
+        <v>107782</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>587</v>
+        <v>585.64</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>102801.54</v>
+        <v>101703.36</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1170.38</v>
+        <v>1167.64</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210734.69</v>
+        <v>209485.36</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.16</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.13</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.81</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81.98</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.89</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.41</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.12</v>
+        <v>78.29000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.23999999999999</v>
+        <v>77.37</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.68000000000001</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.39</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59.33</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.28</v>
+        <v>87.04000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11562,35 +11562,35 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>97.44</v>
+        <v>5356</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,356</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -11602,35 +11602,35 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>95.38</v>
+        <v>779832</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,79,832</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -11642,35 +11642,35 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>95.59999999999999</v>
+        <v>388053</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,88,053</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -11682,35 +11682,35 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>76</v>
+        <v>2683</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,683</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -11722,35 +11722,35 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>92.09999999999999</v>
+        <v>391779</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,91,779</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -11762,35 +11762,35 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>40.7</v>
+        <v>2673</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,673</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -11802,35 +11802,35 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>91.02</v>
+        <v>1132</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,132</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -11842,35 +11842,35 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>83.8</v>
+        <v>193244</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>1,93,244</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -11882,35 +11882,35 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>79.59999999999999</v>
+        <v>87427</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>87,427</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -11922,35 +11922,35 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>49</v>
+        <v>568</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>568</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -11962,35 +11962,35 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>78.45</v>
+        <v>105817</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,05,817</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12002,35 +12002,35 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>80</v>
+        <v>564</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -12042,35 +12042,35 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5393</v>
+        <v>94.25</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>94.25%</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12082,35 +12082,35 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>766540</v>
+        <v>84.91</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>84.91%</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12122,35 +12122,35 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>382785</v>
+        <v>87.8</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>87.80%</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12162,35 +12162,35 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>2695</v>
+        <v>64</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>64.00%</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12202,35 +12202,35 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>383755</v>
+        <v>93.5</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>93.50%</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12242,35 +12242,35 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2698</v>
+        <v>45</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -12282,35 +12282,35 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1175</v>
+        <v>84.91</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>84.91%</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12322,35 +12322,35 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>213994</v>
+        <v>78.5</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>78.50%</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -12362,35 +12362,35 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>105543</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>84.68%</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -12402,35 +12402,35 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>582</v>
+        <v>63</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>63.00%</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -12442,35 +12442,35 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>108451</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.85%</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -12482,38 +12482,998 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>18 August 2026</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>74.60%</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>76</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>49</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>80</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>582</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E289" t="n">
+      <c r="E313" t="n">
         <v>593</v>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F313" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -12530,7 +13490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12807,25 +13767,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>18 August 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="C11" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>84.68000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>63</v>
+      </c>
+      <c r="F11" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>91.02</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>83.8</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>49</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>78.45</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -12840,7 +13825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13127,19 +14112,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>18 August 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>391779</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2673</v>
+      </c>
+      <c r="D15" t="n">
+        <v>105817</v>
+      </c>
+      <c r="E15" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>383755</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>2698</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>108451</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2779.57</v>
+        <v>2778.8</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>392089.71</v>
+        <v>392598.2</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2776.29</v>
+        <v>2775.53</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391457.29</v>
+        <v>391959.53</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5555.86</v>
+        <v>5554.33</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>783547</v>
+        <v>784557.73</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>582</v>
+        <v>580.6</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107782</v>
+        <v>107705.47</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>585.64</v>
+        <v>584.53</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101703.36</v>
+        <v>100701.4</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1167.64</v>
+        <v>1165.13</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>209485.36</v>
+        <v>208406.87</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.48999999999999</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.11</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.93</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.56999999999999</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72.90000000000001</v>
+        <v>71.73</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.79000000000001</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.29000000000001</v>
+        <v>78.44</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.37</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.77</v>
+        <v>82.95</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79.92</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59.7</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.04000000000001</v>
+        <v>86.95999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12522,35 +12522,35 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>97.44</v>
+        <v>5533</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,533</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -12562,35 +12562,35 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>95.38</v>
+        <v>798708</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,98,708</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -12602,35 +12602,35 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>95.59999999999999</v>
+        <v>398991</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,98,991</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -12642,35 +12642,35 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>76</v>
+        <v>2765</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,765</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -12682,35 +12682,35 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>92.09999999999999</v>
+        <v>399717</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,99,717</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -12722,35 +12722,35 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>40.7</v>
+        <v>2768</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,768</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -12762,35 +12762,35 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>91.02</v>
+        <v>1130</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,130</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -12802,35 +12802,35 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>83.8</v>
+        <v>193308</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>1,93,308</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -12842,35 +12842,35 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>79.59999999999999</v>
+        <v>86674</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>86,674</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -12882,35 +12882,35 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>49</v>
+        <v>569</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -12922,35 +12922,35 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>78.45</v>
+        <v>106634</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,06,634</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -12962,35 +12962,35 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>80</v>
+        <v>561</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13002,35 +13002,35 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5393</v>
+        <v>92.47</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>92.47%</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13042,35 +13042,35 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>766540</v>
+        <v>79.7</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>79.70%</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13082,35 +13082,35 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>382785</v>
+        <v>80.42</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>80.42%</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -13122,35 +13122,35 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2695</v>
+        <v>60</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13162,35 +13162,35 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>383755</v>
+        <v>90.3</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13202,35 +13202,35 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2698</v>
+        <v>45</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -13242,35 +13242,35 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1175</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>86.18%</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -13282,35 +13282,35 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>213994</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>82.60%</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -13322,35 +13322,35 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>105543</v>
+        <v>84.3</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>84.30%</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -13362,35 +13362,35 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>582</v>
+        <v>77</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>77.00%</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -13402,35 +13402,35 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>108451</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.90%</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -13442,38 +13442,998 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>19 August 2026</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>84.70%</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>76</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>49</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>80</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>582</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E313" t="n">
+      <c r="E337" t="n">
         <v>593</v>
       </c>
-      <c r="F313" t="inlineStr">
+      <c r="F337" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -13490,7 +14450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13792,25 +14752,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>19 August 2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>91.02</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>83.8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>49</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>78.45</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>80</v>
       </c>
     </row>
@@ -13825,7 +14810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14131,19 +15116,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>19 August 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>399717</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2768</v>
+      </c>
+      <c r="D16" t="n">
+        <v>106634</v>
+      </c>
+      <c r="E16" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>383755</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>2698</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>108451</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2778.8</v>
+        <v>2779.19</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>392598.2</v>
+        <v>393452.88</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2775.53</v>
+        <v>2775.31</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391959.53</v>
+        <v>392908.31</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5554.33</v>
+        <v>5554.5</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>784557.73</v>
+        <v>786361.1899999999</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>580.6</v>
+        <v>580.6900000000001</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107705.47</v>
+        <v>107891</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>584.53</v>
+        <v>584.5599999999999</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100701.4</v>
+        <v>100111.06</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1165.13</v>
+        <v>1165.25</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208406.87</v>
+        <v>208002.06</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.47</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.62</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.03</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.37</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.73</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.94</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.44</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.84999999999999</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.95</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80.31999999999999</v>
+        <v>80.81</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.27</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>86.95999999999999</v>
+        <v>87.12</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13482,35 +13482,35 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>97.44</v>
+        <v>5557</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,557</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -13522,35 +13522,35 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>95.38</v>
+        <v>813413</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,13,413</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -13562,35 +13562,35 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>95.59999999999999</v>
+        <v>407140</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,07,140</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -13602,35 +13602,35 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>76</v>
+        <v>2772</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,772</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -13642,35 +13642,35 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>92.09999999999999</v>
+        <v>406273</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,06,273</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -13682,35 +13682,35 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>40.7</v>
+        <v>2785</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,785</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -13722,35 +13722,35 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>91.02</v>
+        <v>1167</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,167</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -13762,35 +13762,35 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>83.8</v>
+        <v>201930</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,01,930</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -13802,35 +13802,35 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>79.59999999999999</v>
+        <v>91256</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,256</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -13842,35 +13842,35 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>49</v>
+        <v>585</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -13882,35 +13882,35 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>78.45</v>
+        <v>110674</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,10,674</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -13922,35 +13922,35 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -13962,35 +13962,35 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>5393</v>
+        <v>89.41</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.41%</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14002,35 +14002,35 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>766540</v>
+        <v>81.39</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>81.39%</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14042,35 +14042,35 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>382785</v>
+        <v>81.05</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>81.05%</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14082,35 +14082,35 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2695</v>
+        <v>35</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>35.00%</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14122,35 +14122,35 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>383755</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>88.90%</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14162,35 +14162,35 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2698</v>
+        <v>40</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -14202,35 +14202,35 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>1175</v>
+        <v>88.81</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>88.81%</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -14242,35 +14242,35 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>213994</v>
+        <v>86</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>86.00%</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -14282,35 +14282,35 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>105543</v>
+        <v>86.22</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>86.22%</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -14322,35 +14322,35 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>582</v>
+        <v>51</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>51.00%</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -14362,35 +14362,35 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>108451</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>81.60%</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -14402,38 +14402,998 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>20 August 2026</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>83.50%</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>76</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>49</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>80</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>582</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E337" t="n">
+      <c r="E361" t="n">
         <v>593</v>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F361" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -14450,7 +15410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14777,25 +15737,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>20 August 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>91.02</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>83.8</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" t="n">
         <v>49</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>78.45</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>80</v>
       </c>
     </row>
@@ -14810,7 +15795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15135,19 +16120,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>20 August 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>406273</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2785</v>
+      </c>
+      <c r="D17" t="n">
+        <v>110674</v>
+      </c>
+      <c r="E17" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>383755</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>2698</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>108451</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2779.19</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>393452.88</v>
+        <v>395223.35</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2775.31</v>
+        <v>2776.94</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>392908.31</v>
+        <v>394703.65</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5554.5</v>
+        <v>5557.94</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>786361.1899999999</v>
+        <v>789927</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>580.6900000000001</v>
+        <v>582.88</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107891</v>
+        <v>108478.41</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>584.5599999999999</v>
+        <v>585.71</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100111.06</v>
+        <v>100069.29</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1165.25</v>
+        <v>1168.59</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208002.06</v>
+        <v>208547.71</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H361"/>
+  <dimension ref="A1:H373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14442,35 +14442,35 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>97.44</v>
+        <v>5613</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,613</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -14482,35 +14482,35 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>95.38</v>
+        <v>846980</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,46,980</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -14522,35 +14522,35 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>95.59999999999999</v>
+        <v>423429</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,23,429</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -14562,35 +14562,35 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>76</v>
+        <v>2803</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,803</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -14602,35 +14602,35 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>92.09999999999999</v>
+        <v>423551</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,551</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -14642,35 +14642,35 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>40.7</v>
+        <v>2810</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,810</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -14682,35 +14682,35 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>91.02</v>
+        <v>1222</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,222</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -14722,35 +14722,35 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>83.8</v>
+        <v>217278</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,17,278</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -14762,35 +14762,35 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>79.59999999999999</v>
+        <v>99401</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>99,401</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -14802,35 +14802,35 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>49</v>
+        <v>604</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>604</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -14842,35 +14842,35 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>78.45</v>
+        <v>117877</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,17,877</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -14882,35 +14882,35 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -14927,30 +14927,30 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -14967,30 +14967,30 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15007,30 +15007,30 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15047,30 +15047,30 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15087,30 +15087,30 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -15127,30 +15127,30 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -15167,30 +15167,30 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -15207,30 +15207,30 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -15247,30 +15247,30 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -15287,30 +15287,30 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -15327,30 +15327,30 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -15367,33 +15367,513 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>80</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>582</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E361" t="n">
+      <c r="E373" t="n">
         <v>593</v>
       </c>
-      <c r="F361" t="inlineStr">
+      <c r="F373" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -15795,7 +16275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16139,19 +16619,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>22 August 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>423551</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2810</v>
+      </c>
+      <c r="D18" t="n">
+        <v>117877</v>
+      </c>
+      <c r="E18" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>383755</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>2698</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>108451</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2781</v>
+        <v>2784.67</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>395223.35</v>
+        <v>397268.44</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2776.94</v>
+        <v>2780.44</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>394703.65</v>
+        <v>396529.61</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5557.94</v>
+        <v>5565.11</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>789927</v>
+        <v>793798.0600000001</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>582.88</v>
+        <v>584.22</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108478.41</v>
+        <v>109012.89</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>585.71</v>
+        <v>586.83</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100069.29</v>
+        <v>99916</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1168.59</v>
+        <v>1171.06</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208547.71</v>
+        <v>208928.89</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.34</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.34999999999999</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.69</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.26000000000001</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68.67</v>
+        <v>69.38</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.81999999999999</v>
+        <v>91.17</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.7</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78.52</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.98999999999999</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80.81</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.12</v>
+        <v>87.23</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H373"/>
+  <dimension ref="A1:H397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14922,35 +14922,35 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>97.44</v>
+        <v>5687</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,687</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -14962,35 +14962,35 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>95.38</v>
+        <v>859606</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,59,606</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15002,35 +15002,35 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>95.59999999999999</v>
+        <v>427571</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,27,571</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15042,35 +15042,35 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>76</v>
+        <v>2840</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,840</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15082,35 +15082,35 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>92.09999999999999</v>
+        <v>432035</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,32,035</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -15122,35 +15122,35 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>40.7</v>
+        <v>2847</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,847</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -15162,35 +15162,35 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>91.02</v>
+        <v>1213</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,213</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -15202,35 +15202,35 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>83.8</v>
+        <v>215409</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,15,409</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -15242,35 +15242,35 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>79.59999999999999</v>
+        <v>97310</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>97,310</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -15282,35 +15282,35 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>49</v>
+        <v>606</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -15322,35 +15322,35 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>78.45</v>
+        <v>118099</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,18,099</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -15362,35 +15362,35 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -15402,35 +15402,35 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>5393</v>
+        <v>95.45</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>95.45%</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -15442,35 +15442,35 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>766540</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>85.93%</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -15482,35 +15482,35 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>382785</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>81.04%</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -15522,35 +15522,35 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2695</v>
+        <v>78</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>78.00%</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -15562,35 +15562,35 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>383755</v>
+        <v>93</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -15602,35 +15602,35 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2698</v>
+        <v>45</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -15642,35 +15642,35 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>1175</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>88.51%</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -15682,35 +15682,35 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>213994</v>
+        <v>83</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -15722,35 +15722,35 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>105543</v>
+        <v>88.86</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>88.86%</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -15762,35 +15762,35 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>582</v>
+        <v>68</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -15802,35 +15802,35 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>108451</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.85%</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -15842,38 +15842,998 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>23 August 2026</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>90.30%</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>76</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>49</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>80</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>582</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E373" t="n">
+      <c r="E397" t="n">
         <v>593</v>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F397" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -15890,7 +16850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16242,25 +17202,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>23 August 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>83</v>
+      </c>
+      <c r="D14" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>91.02</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>83.8</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>49</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>78.45</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" t="n">
         <v>80</v>
       </c>
     </row>
@@ -16275,7 +17260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16638,19 +17623,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>23 August 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>432035</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2847</v>
+      </c>
+      <c r="D19" t="n">
+        <v>118099</v>
+      </c>
+      <c r="E19" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>383755</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C20" t="n">
         <v>2698</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D20" t="n">
         <v>108451</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2784.67</v>
+        <v>2784.16</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397268.44</v>
+        <v>397274</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2780.44</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396529.61</v>
+        <v>396451.11</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5565.11</v>
+        <v>5563.16</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793798.0600000001</v>
+        <v>793725.11</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>584.22</v>
+        <v>584.37</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109012.89</v>
+        <v>109087</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>586.83</v>
+        <v>587.3200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>99916</v>
+        <v>99371.78999999999</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1171.06</v>
+        <v>1171.68</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208928.89</v>
+        <v>208458.79</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.55</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.47</v>
+        <v>83.61</v>
       </c>
     </row>
     <row r="16">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.17</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69.38</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>91.17</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78.87</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.55</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81.43000000000001</v>
+        <v>81.68000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.23</v>
+        <v>87.03</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H397"/>
+  <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15882,35 +15882,35 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>97.44</v>
+        <v>5528</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -15922,35 +15922,35 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>95.38</v>
+        <v>792412</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -15962,35 +15962,35 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>95.59999999999999</v>
+        <v>395038</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16002,35 +16002,35 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>76</v>
+        <v>2753</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -16042,35 +16042,35 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>92.09999999999999</v>
+        <v>397374</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -16082,35 +16082,35 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>40.7</v>
+        <v>2775</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -16122,35 +16122,35 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>91.02</v>
+        <v>1183</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -16162,35 +16162,35 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>83.8</v>
+        <v>199997</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -16202,35 +16202,35 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>79.59999999999999</v>
+        <v>89576</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -16242,35 +16242,35 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>49</v>
+        <v>596</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -16282,35 +16282,35 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>78.45</v>
+        <v>110421</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -16322,35 +16322,35 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>80</v>
+        <v>587</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -16362,35 +16362,35 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>5393</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -16402,35 +16402,35 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>766540</v>
+        <v>72.42</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -16442,35 +16442,35 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>382785</v>
+        <v>63.55</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -16482,35 +16482,35 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>2695</v>
+        <v>80</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -16522,35 +16522,35 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>383755</v>
+        <v>82.5</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -16562,35 +16562,35 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2698</v>
+        <v>43.8</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -16602,35 +16602,35 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>1175</v>
+        <v>84.47</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -16642,35 +16642,35 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>213994</v>
+        <v>81.5</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -16682,35 +16682,35 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>105543</v>
+        <v>84.98</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -16722,35 +16722,35 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>582</v>
+        <v>65</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -16762,35 +16762,35 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>108451</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -16802,38 +16802,998 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>24 August 2026</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>80.80%</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>76</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>49</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>80</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>582</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E397" t="n">
+      <c r="E421" t="n">
         <v>593</v>
       </c>
-      <c r="F397" t="inlineStr">
+      <c r="F421" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -16850,7 +17810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17227,25 +18187,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>24 August 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="C15" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="E15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F15" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>91.02</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>83.8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>49</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>78.45</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>80</v>
       </c>
     </row>
@@ -17260,7 +18245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17642,19 +18627,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>24 August 2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>397374</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2775</v>
+      </c>
+      <c r="D20" t="n">
+        <v>110421</v>
+      </c>
+      <c r="E20" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>383755</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>2698</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>108451</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2784.16</v>
+        <v>2784.35</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397274</v>
+        <v>398189.6</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2779</v>
+        <v>2779.45</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396451.11</v>
+        <v>397548.35</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5563.16</v>
+        <v>5563.8</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793725.11</v>
+        <v>795737.95</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>584.37</v>
+        <v>583.6</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109087</v>
+        <v>109047.35</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>587.3200000000001</v>
+        <v>586.55</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>99371.78999999999</v>
+        <v>98509.64999999999</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1171.68</v>
+        <v>1170.15</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208458.79</v>
+        <v>207557</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.97</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.61</v>
+        <v>84.27</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.79</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.84</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.14</v>
+        <v>71.06999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.44</v>
+        <v>90.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.17</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.06</v>
+        <v>79.22</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.36</v>
+        <v>83.31</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81.68000000000001</v>
+        <v>82.06</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.29</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.03</v>
+        <v>87.13</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16842,35 +16842,35 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>97.44</v>
+        <v>5576</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -16882,35 +16882,35 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>95.38</v>
+        <v>833982</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -16922,35 +16922,35 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>95.59999999999999</v>
+        <v>418396</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -16962,35 +16962,35 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>76</v>
+        <v>2788</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -17002,35 +17002,35 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>92.09999999999999</v>
+        <v>415586</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -17042,35 +17042,35 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>40.7</v>
+        <v>2788</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -17082,35 +17082,35 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>91.02</v>
+        <v>1141</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -17122,35 +17122,35 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>83.8</v>
+        <v>190423</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -17162,35 +17162,35 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>79.59999999999999</v>
+        <v>82129</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -17202,35 +17202,35 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>49</v>
+        <v>572</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -17242,35 +17242,35 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>78.45</v>
+        <v>108294</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -17282,35 +17282,35 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>80</v>
+        <v>569</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -17322,35 +17322,35 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>5393</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -17362,35 +17362,35 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>766540</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -17402,35 +17402,35 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>382785</v>
+        <v>74.27</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -17442,35 +17442,35 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>2695</v>
+        <v>84</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -17482,35 +17482,35 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -17522,35 +17522,35 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>2698</v>
+        <v>30.8</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -17562,35 +17562,35 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1175</v>
+        <v>88.58</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -17602,35 +17602,35 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>213994</v>
+        <v>81.5</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -17642,35 +17642,35 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>105543</v>
+        <v>87.28</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -17682,35 +17682,35 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>582</v>
+        <v>75</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -17722,35 +17722,35 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>108451</v>
+        <v>84.11</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -17762,38 +17762,998 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>26 August 2026</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>82.70%</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>76</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>49</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>80</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>582</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E421" t="n">
+      <c r="E445" t="n">
         <v>593</v>
       </c>
-      <c r="F421" t="inlineStr">
+      <c r="F445" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr">
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -17810,7 +18770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18212,25 +19172,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>26 August 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="C16" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="E16" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>91.02</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>83.8</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>49</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>78.45</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" t="n">
         <v>80</v>
       </c>
     </row>
@@ -18245,7 +19230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18646,19 +19631,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>26 August 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>415586</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2788</v>
+      </c>
+      <c r="D21" t="n">
+        <v>108294</v>
+      </c>
+      <c r="E21" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>383755</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2698</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>108451</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2784.35</v>
+        <v>2787.57</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>398189.6</v>
+        <v>399396.76</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2779.45</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>397548.35</v>
+        <v>398371</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5563.8</v>
+        <v>5569.57</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>795737.95</v>
+        <v>797767.76</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>583.6</v>
+        <v>584.71</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109047.35</v>
+        <v>109672.95</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>586.55</v>
+        <v>587.71</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>98509.64999999999</v>
+        <v>98154.81</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1170.15</v>
+        <v>1172.43</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>207557</v>
+        <v>207827.76</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.11</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.27</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42.93</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.40000000000001</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.06999999999999</v>
+        <v>71.12</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.43000000000001</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.5</v>
+        <v>79.83</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.22</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.31</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82.06</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.2</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.13</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H445"/>
+  <dimension ref="A1:H469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17802,35 +17802,35 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -17842,35 +17842,35 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -17882,35 +17882,35 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -17922,35 +17922,35 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -17962,35 +17962,35 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -18002,35 +18002,35 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -18042,35 +18042,35 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -18082,35 +18082,35 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -18122,35 +18122,35 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -18162,35 +18162,35 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -18202,35 +18202,35 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -18242,35 +18242,35 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -18282,35 +18282,35 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -18322,35 +18322,35 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -18362,35 +18362,35 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -18402,35 +18402,35 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -18442,35 +18442,35 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -18482,35 +18482,35 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -18522,35 +18522,35 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -18562,35 +18562,35 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -18602,35 +18602,35 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -18642,35 +18642,35 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -18682,35 +18682,35 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -18722,38 +18722,998 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>92.20%</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>76</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>49</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>80</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>582</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E445" t="n">
+      <c r="E469" t="n">
         <v>593</v>
       </c>
-      <c r="F445" t="inlineStr">
+      <c r="F469" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -18770,7 +19730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19197,25 +20157,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="C17" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>72</v>
+      </c>
+      <c r="F17" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>91.02</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>83.8</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>49</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>78.45</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>80</v>
       </c>
     </row>
@@ -19230,7 +20215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19650,19 +20635,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>423540</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2852</v>
+      </c>
+      <c r="D22" t="n">
+        <v>122185</v>
+      </c>
+      <c r="E22" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>383755</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>2698</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>108451</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2787.57</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>399396.76</v>
+        <v>390487</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2782</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>398371</v>
+        <v>395228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5569.57</v>
+        <v>5499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>797767.76</v>
+        <v>785715</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>584.71</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109672.95</v>
+        <v>115412</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>587.71</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>98154.81</v>
+        <v>83567</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1172.43</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>207827.76</v>
+        <v>198979</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.38</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.77</v>
+        <v>92.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42.82</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.19</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -790,13 +790,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.38</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.83</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.47</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.87</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82.37</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.40000000000001</v>
+        <v>85.66</v>
       </c>
     </row>
   </sheetData>
@@ -944,11 +944,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H469"/>
+  <dimension ref="A1:H493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -13482,12 +13482,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -13501,11 +13501,11 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>5557</v>
+        <v>5499</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>5,557</t>
+          <t>5,499</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -13522,12 +13522,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -13541,11 +13541,11 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>813413</v>
+        <v>785715</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>8,13,413</t>
+          <t>7,85,715</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -13562,12 +13562,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -13581,11 +13581,11 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>407140</v>
+        <v>395228</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>4,07,140</t>
+          <t>3,95,228</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -13602,12 +13602,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -13621,11 +13621,11 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2772</v>
+        <v>2750</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2,772</t>
+          <t>2,750</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -13642,12 +13642,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -13661,11 +13661,11 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>406273</v>
+        <v>390487</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>4,06,273</t>
+          <t>3,90,487</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -13682,12 +13682,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -13701,11 +13701,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2785</v>
+        <v>2749</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2,785</t>
+          <t>2,749</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -13722,12 +13722,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -13741,11 +13741,11 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>1167</v>
+        <v>1189</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1,167</t>
+          <t>1,189</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -13762,12 +13762,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -13781,11 +13781,11 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>201930</v>
+        <v>198979</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2,01,930</t>
+          <t>1,98,979</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -13802,12 +13802,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -13821,11 +13821,11 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>91256</v>
+        <v>83567</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>91,256</t>
+          <t>83,567</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -13842,12 +13842,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -13861,11 +13861,11 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -13882,12 +13882,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -13901,11 +13901,11 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>110674</v>
+        <v>115412</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1,10,674</t>
+          <t>1,15,412</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -13922,12 +13922,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -13941,11 +13941,11 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>592</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -13962,12 +13962,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -13981,11 +13981,11 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>89.41</v>
+        <v>98.94</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>89.41%</t>
+          <t>98.94%</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -14002,12 +14002,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14021,11 +14021,11 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>81.39</v>
+        <v>92.63</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>81.39%</t>
+          <t>92.63%</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -14042,12 +14042,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14061,11 +14061,11 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>81.05</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>81.05%</t>
+          <t>83.68%</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -14082,12 +14082,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14101,11 +14101,11 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>35.00%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -14122,12 +14122,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14141,11 +14141,11 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>88.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>88.90%</t>
+          <t>93.10%</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -14162,12 +14162,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14181,11 +14181,11 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>41.70%</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -14202,12 +14202,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14221,11 +14221,11 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>88.81</v>
+        <v>85.66</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>88.81%</t>
+          <t>85.66%</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -14242,12 +14242,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -14261,11 +14261,11 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>86</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>86.00%</t>
+          <t>80.10%</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -14282,12 +14282,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -14301,11 +14301,11 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>86.22</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>86.22%</t>
+          <t>80.85%</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -14322,12 +14322,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -14341,11 +14341,11 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>51.00%</t>
+          <t>67.00%</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -14362,12 +14362,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -14381,11 +14381,11 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>81.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>81.60%</t>
+          <t>80.50%</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -14402,12 +14402,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -14421,11 +14421,11 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>83.5</v>
+        <v>88.2</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>83.50%</t>
+          <t>88.20%</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -14442,12 +14442,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14461,11 +14461,11 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>5613</v>
+        <v>5557</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>5,613</t>
+          <t>5,557</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -14482,12 +14482,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14501,11 +14501,11 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>846980</v>
+        <v>813413</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>8,46,980</t>
+          <t>8,13,413</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -14522,12 +14522,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14541,11 +14541,11 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>423429</v>
+        <v>407140</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>4,23,429</t>
+          <t>4,07,140</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -14562,12 +14562,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14581,11 +14581,11 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>2803</v>
+        <v>2772</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2,803</t>
+          <t>2,772</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -14602,12 +14602,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14621,11 +14621,11 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>423551</v>
+        <v>406273</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>4,23,551</t>
+          <t>4,06,273</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -14642,12 +14642,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14661,11 +14661,11 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2810</v>
+        <v>2785</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2,810</t>
+          <t>2,785</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -14682,12 +14682,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14701,11 +14701,11 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>1222</v>
+        <v>1167</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>1,222</t>
+          <t>1,167</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -14722,12 +14722,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -14741,11 +14741,11 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>217278</v>
+        <v>201930</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2,17,278</t>
+          <t>2,01,930</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -14762,12 +14762,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14781,11 +14781,11 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>99401</v>
+        <v>91256</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>99,401</t>
+          <t>91,256</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -14802,12 +14802,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14821,11 +14821,11 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -14842,12 +14842,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -14861,11 +14861,11 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>117877</v>
+        <v>110674</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>1,17,877</t>
+          <t>1,10,674</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -14882,12 +14882,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -14901,11 +14901,11 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>618</v>
+        <v>582</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -14922,35 +14922,35 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>5687</v>
+        <v>89.41</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>5,687</t>
+          <t>89.41%</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -14962,35 +14962,35 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>859606</v>
+        <v>81.39</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>8,59,606</t>
+          <t>81.39%</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15002,35 +15002,35 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>427571</v>
+        <v>81.05</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>4,27,571</t>
+          <t>81.05%</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15042,35 +15042,35 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2840</v>
+        <v>35</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2,840</t>
+          <t>35.00%</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15082,35 +15082,35 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>432035</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>4,32,035</t>
+          <t>88.90%</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -15122,35 +15122,35 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2847</v>
+        <v>40</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2,847</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -15162,35 +15162,35 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1213</v>
+        <v>88.81</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>1,213</t>
+          <t>88.81%</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -15202,35 +15202,35 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>215409</v>
+        <v>86</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2,15,409</t>
+          <t>86.00%</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -15242,35 +15242,35 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>97310</v>
+        <v>86.22</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>97,310</t>
+          <t>86.22%</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -15282,35 +15282,35 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>606</v>
+        <v>51</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>51.00%</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -15322,35 +15322,35 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>118099</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>1,18,099</t>
+          <t>81.60%</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -15362,35 +15362,35 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>607</v>
+        <v>83.5</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>83.50%</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -15402,35 +15402,35 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>95.45</v>
+        <v>5613</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>95.45%</t>
+          <t>5,613</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -15442,35 +15442,35 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>85.93000000000001</v>
+        <v>846980</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>85.93%</t>
+          <t>8,46,980</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -15482,35 +15482,35 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>81.04000000000001</v>
+        <v>423429</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>81.04%</t>
+          <t>4,23,429</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -15522,35 +15522,35 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>78</v>
+        <v>2803</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>78.00%</t>
+          <t>2,803</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -15562,35 +15562,35 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>93</v>
+        <v>423551</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>93.00%</t>
+          <t>4,23,551</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -15602,35 +15602,35 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>45</v>
+        <v>2810</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>2,810</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -15642,35 +15642,35 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>88.51000000000001</v>
+        <v>1222</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>88.51%</t>
+          <t>1,222</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -15682,35 +15682,35 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>83</v>
+        <v>217278</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>83.00%</t>
+          <t>2,17,278</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -15722,35 +15722,35 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>88.86</v>
+        <v>99401</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>88.86%</t>
+          <t>99,401</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -15762,35 +15762,35 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>68</v>
+        <v>604</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>604</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -15802,35 +15802,35 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>84.84999999999999</v>
+        <v>117877</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>84.85%</t>
+          <t>1,17,877</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -15842,35 +15842,35 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>90.3</v>
+        <v>618</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>90.30%</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -15882,12 +15882,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -15901,11 +15901,11 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>5528</v>
+        <v>5687</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>5,687</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -15922,12 +15922,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15941,11 +15941,11 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>792412</v>
+        <v>859606</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>7,92,412</t>
+          <t>8,59,606</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -15962,12 +15962,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15981,11 +15981,11 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>395038</v>
+        <v>427571</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>3,95,038</t>
+          <t>4,27,571</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -16002,12 +16002,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16021,11 +16021,11 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2753</v>
+        <v>2840</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,840</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -16042,12 +16042,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -16061,11 +16061,11 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>3,97,374</t>
+          <t>4,32,035</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -16082,12 +16082,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16101,11 +16101,11 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2,775</t>
+          <t>2,847</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -16122,12 +16122,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16141,11 +16141,11 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>1,213</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -16162,12 +16162,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16181,11 +16181,11 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>199997</v>
+        <v>215409</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>1,99,997</t>
+          <t>2,15,409</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -16202,12 +16202,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16221,11 +16221,11 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>89576</v>
+        <v>97310</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>89,576</t>
+          <t>97,310</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -16242,12 +16242,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16261,11 +16261,11 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -16282,12 +16282,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16301,11 +16301,11 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>1,10,421</t>
+          <t>1,18,099</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -16322,12 +16322,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16341,11 +16341,11 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -16362,12 +16362,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16381,11 +16381,11 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>80.90000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>80.90%</t>
+          <t>95.45%</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -16402,12 +16402,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16421,11 +16421,11 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>72.42</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>72.42%</t>
+          <t>85.93%</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -16442,12 +16442,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16461,11 +16461,11 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>63.55</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>63.55%</t>
+          <t>81.04%</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -16482,12 +16482,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16501,11 +16501,11 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>78.00%</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -16522,12 +16522,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16541,11 +16541,11 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>82.5</v>
+        <v>93</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>82.50%</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -16562,12 +16562,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16581,11 +16581,11 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>43.80%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -16602,12 +16602,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16621,11 +16621,11 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>84.47%</t>
+          <t>88.51%</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -16642,12 +16642,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16661,11 +16661,11 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -16682,12 +16682,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -16701,11 +16701,11 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>84.98%</t>
+          <t>88.86%</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -16722,12 +16722,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -16741,11 +16741,11 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>65.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -16762,12 +16762,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -16781,11 +16781,11 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>79.10%</t>
+          <t>84.85%</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -16802,12 +16802,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -16821,11 +16821,11 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>80.80%</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -16842,12 +16842,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -16861,11 +16861,11 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>5576</v>
+        <v>5528</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -16882,12 +16882,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -16901,11 +16901,11 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>833982</v>
+        <v>792412</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -16922,12 +16922,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -16941,11 +16941,11 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>418396</v>
+        <v>395038</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -16962,12 +16962,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -16981,11 +16981,11 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>2788</v>
+        <v>2753</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -17002,12 +17002,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17021,11 +17021,11 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -17042,12 +17042,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -17061,11 +17061,11 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -17082,12 +17082,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17101,11 +17101,11 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1141</v>
+        <v>1183</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -17122,12 +17122,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17141,11 +17141,11 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>190423</v>
+        <v>199997</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -17162,12 +17162,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17181,11 +17181,11 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>82129</v>
+        <v>89576</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -17202,12 +17202,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17221,11 +17221,11 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -17242,12 +17242,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17261,11 +17261,11 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -17282,12 +17282,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -17301,11 +17301,11 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -17322,12 +17322,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17341,11 +17341,11 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>90.31999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -17362,12 +17362,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17381,11 +17381,11 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>93.51000000000001</v>
+        <v>72.42</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -17402,12 +17402,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17421,11 +17421,11 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>74.27</v>
+        <v>63.55</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -17442,12 +17442,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -17461,11 +17461,11 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -17482,12 +17482,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -17501,11 +17501,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>92.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -17522,12 +17522,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -17541,11 +17541,11 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -17562,12 +17562,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17581,11 +17581,11 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -17602,12 +17602,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17642,12 +17642,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17661,11 +17661,11 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -17682,12 +17682,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17701,11 +17701,11 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -17722,12 +17722,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17741,11 +17741,11 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -17762,12 +17762,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17781,11 +17781,11 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>80.80%</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -17802,12 +17802,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -17821,11 +17821,11 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5685</v>
+        <v>5576</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -17842,12 +17842,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17861,11 +17861,11 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>838364</v>
+        <v>833982</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -17882,12 +17882,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -17901,11 +17901,11 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>414824</v>
+        <v>418396</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -17922,12 +17922,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -17941,11 +17941,11 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>2833</v>
+        <v>2788</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -17962,12 +17962,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -17981,11 +17981,11 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -18002,12 +18002,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -18021,11 +18021,11 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -18042,12 +18042,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -18061,11 +18061,11 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>1218</v>
+        <v>1141</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -18082,12 +18082,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -18101,11 +18101,11 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>213243</v>
+        <v>190423</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -18122,12 +18122,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -18141,11 +18141,11 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>91058</v>
+        <v>82129</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -18162,12 +18162,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -18181,11 +18181,11 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -18202,12 +18202,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -18221,11 +18221,11 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -18242,12 +18242,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -18261,11 +18261,11 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -18282,12 +18282,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -18301,11 +18301,11 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>89.66</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -18322,12 +18322,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -18341,11 +18341,11 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>92.28</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -18362,12 +18362,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18381,11 +18381,11 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>77.13</v>
+        <v>74.27</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -18402,12 +18402,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -18421,11 +18421,11 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -18442,12 +18442,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -18461,11 +18461,11 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -18482,12 +18482,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -18501,11 +18501,11 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>41.2</v>
+        <v>30.8</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -18522,12 +18522,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -18541,11 +18541,11 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -18562,12 +18562,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18581,11 +18581,11 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -18602,12 +18602,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18621,11 +18621,11 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -18642,12 +18642,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18661,11 +18661,11 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -18682,12 +18682,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -18701,11 +18701,11 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -18722,12 +18722,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -18741,11 +18741,11 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -18762,35 +18762,35 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -18802,35 +18802,35 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -18842,35 +18842,35 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -18882,35 +18882,35 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -18922,35 +18922,35 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -18962,35 +18962,35 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -19002,35 +19002,35 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -19042,35 +19042,35 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -19082,35 +19082,35 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -19122,35 +19122,35 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -19162,35 +19162,35 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -19202,35 +19202,35 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -19242,35 +19242,35 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -19282,35 +19282,35 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -19322,35 +19322,35 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -19362,35 +19362,35 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -19402,35 +19402,35 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -19442,35 +19442,35 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -19482,35 +19482,35 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -19522,35 +19522,35 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -19562,35 +19562,35 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -19602,35 +19602,35 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -19642,35 +19642,35 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -19682,38 +19682,998 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>92.20%</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>97.44%</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>95.38%</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>95.60%</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>76</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>76.00%</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>92.10%</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>40.70%</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>91.02%</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>83.80%</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>79.60%</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>49</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>78.45%</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>30 July 2026</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>80</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
         <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>5393</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>5,393</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>766540</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>7,66,540</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>382785</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>3,82,785</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2,695</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>383755</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>3,83,755</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
         <is>
           <t>International traffic</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr">
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>213994</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2,13,994</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>105543</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>1,05,543</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>582</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>108451</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>1,08,451</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>31 July 2026</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
         <is>
           <t>Departing flights</t>
         </is>
       </c>
-      <c r="E469" t="n">
+      <c r="E493" t="n">
         <v>593</v>
       </c>
-      <c r="F469" t="inlineStr">
+      <c r="F493" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H469" t="inlineStr">
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -19730,10 +20690,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -20057,150 +21017,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88.81</v>
+        <v>85.66</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>86.22</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>81.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="G13" t="n">
-        <v>83.5</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88.51000000000001</v>
+        <v>88.81</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>88.86</v>
+        <v>86.22</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>84.84999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>90.3</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="D15" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="C16" t="n">
         <v>81.5</v>
       </c>
       <c r="D16" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C17" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D17" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G17" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>72</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>30 July 2026</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>91.02</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>83.8</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>49</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>78.45</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>80</v>
       </c>
     </row>
@@ -20215,10 +21200,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -20540,133 +21525,152 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>2 September 2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>406273</v>
+        <v>390487</v>
       </c>
       <c r="C17" t="n">
-        <v>2785</v>
+        <v>2749</v>
       </c>
       <c r="D17" t="n">
-        <v>110674</v>
+        <v>115412</v>
       </c>
       <c r="E17" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>423551</v>
+        <v>406273</v>
       </c>
       <c r="C18" t="n">
-        <v>2810</v>
+        <v>2785</v>
       </c>
       <c r="D18" t="n">
-        <v>117877</v>
+        <v>110674</v>
       </c>
       <c r="E18" t="n">
-        <v>618</v>
+        <v>582</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>432035</v>
+        <v>423551</v>
       </c>
       <c r="C19" t="n">
-        <v>2847</v>
+        <v>2810</v>
       </c>
       <c r="D19" t="n">
-        <v>118099</v>
+        <v>117877</v>
       </c>
       <c r="E19" t="n">
-        <v>607</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="C20" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="D20" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="E20" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="C21" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="D21" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="E21" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="C22" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="D22" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="E22" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>423540</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2852</v>
+      </c>
+      <c r="D23" t="n">
+        <v>122185</v>
+      </c>
+      <c r="E23" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>31 July 2026</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
         <v>383755</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C24" t="n">
         <v>2698</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>108451</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>593</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2749</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>390487</v>
+        <v>391219.5</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2750</v>
+        <v>2751.5</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>395228</v>
+        <v>392467.5</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5499</v>
+        <v>5515.5</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>785715</v>
+        <v>783687</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>592</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115412</v>
+        <v>118448</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>597</v>
+        <v>601.5</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83567</v>
+        <v>86933</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1189</v>
+        <v>1211.5</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>198979</v>
+        <v>205381</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H493"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20674,6 +20674,486 @@
         </is>
       </c>
       <c r="H493" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>5532</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>5,532</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>781659</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>7,81,659</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>389707</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>3,89,707</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>2753</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2,753</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>391952</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>3,91,952</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2,779</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>1,234</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>211783</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2,11,783</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>90299</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>90,299</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>606</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>121484</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>1,21,484</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>628</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -21200,7 +21680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21674,6 +22154,25 @@
         <v>593</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>391952</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2779</v>
+      </c>
+      <c r="D25" t="n">
+        <v>121484</v>
+      </c>
+      <c r="E25" t="n">
+        <v>628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2764</v>
+        <v>2768.67</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>391219.5</v>
+        <v>391179.67</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2751.5</v>
+        <v>2764.33</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>392467.5</v>
+        <v>392317.33</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5515.5</v>
+        <v>5533</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>783687</v>
+        <v>783497</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>118448</v>
+        <v>118770.67</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>601.5</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86933</v>
+        <v>90567.33</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1211.5</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>205381</v>
+        <v>209338</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H505"/>
+  <dimension ref="A1:H517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21154,6 +21154,486 @@
         </is>
       </c>
       <c r="H505" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>5568</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>5,568</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>783117</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>7,83,117</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>392017</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>3,92,017</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>2790</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2,790</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>391100</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>3,91,100</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>2778</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2,778</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>1,243</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>217252</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2,17,252</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>97836</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>97,836</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>633</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>119416</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>1,19,416</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>610</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -21680,7 +22160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22173,6 +22653,25 @@
         <v>628</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5 September 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>391100</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D26" t="n">
+        <v>119416</v>
+      </c>
+      <c r="E26" t="n">
+        <v>610</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
